--- a/public/manifest_template.xlsx
+++ b/public/manifest_template.xlsx
@@ -5,19 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Projects\go-report\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Projects\go-report\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F29536E-34DC-4A58-8A66-A04E3E9EB77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2A9B40E6-AF92-4CA7-8CA0-0EBB4247B14C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
-    <sheet name="JKT" sheetId="1" r:id="rId1"/>
-    <sheet name="JAT" sheetId="3" r:id="rId2"/>
+    <sheet name="TEMPLATE" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId2"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
   <si>
     <t>BTN GATEWAY</t>
   </si>
@@ -121,59 +119,439 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>LE21735033</t>
+  </si>
+  <si>
+    <t>EZ</t>
+  </si>
+  <si>
+    <t>LE21767911</t>
+  </si>
+  <si>
+    <t>LE21666060</t>
+  </si>
+  <si>
+    <t>LE21609351</t>
+  </si>
+  <si>
+    <t>LE21666695</t>
+  </si>
+  <si>
+    <t>LE20821676</t>
+  </si>
+  <si>
+    <t>LE21547955</t>
+  </si>
+  <si>
+    <t>LE21952018</t>
+  </si>
+  <si>
+    <t>LE21669020</t>
+  </si>
+  <si>
+    <t>LE21545695</t>
+  </si>
+  <si>
+    <t>LE21893303</t>
+  </si>
+  <si>
+    <t>LE21737109</t>
+  </si>
+  <si>
+    <t>LE21732627</t>
+  </si>
+  <si>
+    <t>LE21365607</t>
+  </si>
+  <si>
+    <t>LE21572305</t>
+  </si>
+  <si>
+    <t>LE20503355</t>
+  </si>
+  <si>
+    <t>LE21624725</t>
+  </si>
+  <si>
+    <t>LE21990298</t>
+  </si>
+  <si>
+    <t>LE21571910</t>
+  </si>
+  <si>
+    <t>LE21720855</t>
+  </si>
+  <si>
+    <t>LE21846605</t>
+  </si>
+  <si>
+    <t>LE21583393</t>
+  </si>
+  <si>
+    <t>LE21707779</t>
+  </si>
+  <si>
+    <t>LE21210682</t>
+  </si>
+  <si>
+    <t>LE21774440</t>
+  </si>
+  <si>
+    <t>LE21686094</t>
+  </si>
+  <si>
+    <t>LE21718366</t>
+  </si>
+  <si>
+    <t>LE21657092</t>
+  </si>
+  <si>
+    <t>LE20811545</t>
+  </si>
+  <si>
+    <t>F10291369</t>
+  </si>
+  <si>
+    <t>LE21618282</t>
+  </si>
+  <si>
+    <t>LE21666944</t>
+  </si>
+  <si>
+    <t>LE21924940</t>
+  </si>
+  <si>
+    <t>F06911597</t>
+  </si>
+  <si>
+    <t>LE21754420</t>
+  </si>
+  <si>
+    <t>LE21998645</t>
+  </si>
+  <si>
+    <t>LE21955834</t>
+  </si>
+  <si>
+    <t>LE21986062</t>
+  </si>
+  <si>
+    <t>LE20851374</t>
+  </si>
+  <si>
+    <t>LE21979354</t>
+  </si>
+  <si>
+    <t>LE21687330</t>
+  </si>
+  <si>
+    <t>LE21633679</t>
+  </si>
+  <si>
+    <t>LE21709548</t>
+  </si>
+  <si>
+    <t>LE21772780</t>
+  </si>
+  <si>
+    <t>LE21656989</t>
+  </si>
+  <si>
+    <t>LE21580852</t>
+  </si>
+  <si>
+    <t>LE21652580</t>
+  </si>
+  <si>
+    <t>LE21734658</t>
+  </si>
+  <si>
+    <t>LE21625517</t>
+  </si>
+  <si>
+    <t>LE21955895</t>
+  </si>
+  <si>
+    <t>LE21554075</t>
+  </si>
+  <si>
+    <t>LE21618454</t>
+  </si>
+  <si>
+    <t>LE21867064</t>
+  </si>
+  <si>
+    <t>LE22004503</t>
+  </si>
+  <si>
+    <t>LE21638270</t>
+  </si>
+  <si>
+    <t>LE21848415</t>
+  </si>
+  <si>
+    <t>LE21672104</t>
+  </si>
+  <si>
+    <t>LE19400403</t>
+  </si>
+  <si>
+    <t>F06911566</t>
+  </si>
+  <si>
+    <t>LE21586072</t>
+  </si>
+  <si>
+    <t>LE21549556</t>
+  </si>
+  <si>
+    <t>LE21660884</t>
+  </si>
+  <si>
+    <t>LE21635568</t>
+  </si>
+  <si>
+    <t>LE21573663</t>
+  </si>
+  <si>
+    <t>LE21769697</t>
+  </si>
+  <si>
+    <t>LE21585223</t>
+  </si>
+  <si>
+    <t>LE21659521</t>
+  </si>
+  <si>
+    <t>LE21461966</t>
+  </si>
+  <si>
+    <t>LE21568144</t>
+  </si>
+  <si>
+    <t>LE21886290</t>
+  </si>
+  <si>
+    <t>F07078177</t>
+  </si>
+  <si>
+    <t>LE21755772</t>
+  </si>
+  <si>
+    <t>LE21673945</t>
+  </si>
+  <si>
+    <t>LE22034463</t>
+  </si>
+  <si>
+    <t>LE21897986</t>
+  </si>
+  <si>
+    <t>LE21642830</t>
+  </si>
+  <si>
+    <t>LE21901893</t>
+  </si>
+  <si>
+    <t>LE21758090</t>
+  </si>
+  <si>
+    <t>F06950533</t>
+  </si>
+  <si>
+    <t>LE21766935</t>
+  </si>
+  <si>
+    <t>LE21647659</t>
+  </si>
+  <si>
+    <t>LE21764062</t>
+  </si>
+  <si>
+    <t>LE21895451</t>
+  </si>
+  <si>
+    <t>LE21647176</t>
+  </si>
+  <si>
+    <t>LE21446642</t>
+  </si>
+  <si>
+    <t>LE21695404</t>
+  </si>
+  <si>
+    <t>LE21997445</t>
+  </si>
+  <si>
+    <t>LE21701655</t>
+  </si>
+  <si>
+    <t>LE21655828</t>
+  </si>
+  <si>
+    <t>LE21572200</t>
+  </si>
+  <si>
+    <t>LE21579239</t>
+  </si>
+  <si>
+    <t>LE21923220</t>
+  </si>
+  <si>
+    <t>LE21670560</t>
+  </si>
+  <si>
+    <t>LE21749912</t>
+  </si>
+  <si>
+    <t>LE21586571</t>
+  </si>
+  <si>
+    <t>LE21640971</t>
+  </si>
+  <si>
+    <t>LE21637424</t>
+  </si>
+  <si>
+    <t>LE21767076</t>
+  </si>
+  <si>
+    <t>LE21530251</t>
+  </si>
+  <si>
+    <t>LE21688757</t>
+  </si>
+  <si>
+    <t>LE21563739</t>
+  </si>
+  <si>
+    <t>LE21553982</t>
+  </si>
+  <si>
+    <t>LE21661245</t>
+  </si>
+  <si>
+    <t>LE21693743</t>
+  </si>
+  <si>
+    <t>LE21693977</t>
+  </si>
+  <si>
+    <t>LE21947492</t>
+  </si>
+  <si>
+    <t>LE21790005</t>
+  </si>
+  <si>
+    <t>LE21643149</t>
+  </si>
+  <si>
+    <t>F10291368</t>
+  </si>
+  <si>
+    <t>LE21585387</t>
+  </si>
+  <si>
+    <t>LE21674683</t>
+  </si>
+  <si>
+    <t>LE21669151</t>
+  </si>
+  <si>
+    <t>LE21662488</t>
+  </si>
+  <si>
+    <t>LE21995147</t>
+  </si>
+  <si>
+    <t>LE21589886</t>
+  </si>
+  <si>
+    <t>LE21649918</t>
+  </si>
+  <si>
+    <t>LE21570475</t>
+  </si>
+  <si>
+    <t>LE21648541</t>
+  </si>
+  <si>
+    <t>E58239886</t>
+  </si>
+  <si>
+    <t>LE21700219</t>
+  </si>
+  <si>
+    <t>LE21946085</t>
+  </si>
+  <si>
+    <t>LE21673217</t>
+  </si>
+  <si>
+    <t>LE21662996</t>
+  </si>
+  <si>
+    <t>E58239887</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="20"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="20"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Roboto Condensed"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Roboto Condensed"/>
     </font>
     <font>
-      <b/>
+      <name val="Roboto Condensed"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Roboto Condensed"/>
     </font>
     <font>
-      <b/>
-      <i/>
+      <name val="Roboto Condensed"/>
+      <b val="1"/>
+      <i val="1"/>
       <sz val="11"/>
-      <name val="Roboto Condensed"/>
     </font>
     <font>
-      <b/>
+      <name val="Roboto Condensed"/>
+      <b val="1"/>
       <sz val="82"/>
-      <name val="Roboto Condensed"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color/>
     </font>
   </fonts>
   <fills count="8">
@@ -185,19 +563,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79995117038483843"/>
+        <fgColor theme="5" tint="0.7999511703848384"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -215,12 +593,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39994506668294322"/>
+        <fgColor theme="5" tint="0.3999450666829432"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -230,14 +608,14 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right/>
       <top style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
@@ -245,50 +623,50 @@
       <left/>
       <right/>
       <top style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -296,262 +674,149 @@
     <border>
       <left/>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" quotePrefix="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment textRotation="90" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment textRotation="90" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -683,7 +948,7 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -696,7 +961,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -711,51 +976,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{202116B4-4593-4F20-AF48-402399F56C1E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect l="2725" t="12993" r="10856" b="14810"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6076950" y="0"/>
-          <a:ext cx="1413855" cy="801414"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1413855" cy="801414"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0F728BB-43D5-4904-A684-A651E921DA09}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -829,7 +1049,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1146,17 +1366,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41617E2A-008F-44DF-8B40-2878E57D286B}">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" customWidth="1"/>
-    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="12"/>
+    <col customWidth="true" max="2" min="2" width="15.42578125"/>
+    <col customWidth="true" max="3" min="3" width="19.5703125"/>
+    <col customWidth="true" max="4" min="4" width="19"/>
+    <col customWidth="true" max="5" min="5" width="20.5703125"/>
+    <col customWidth="true" max="6" min="6" width="25.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="18.75">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1166,7 +1386,7 @@
       <c r="E1" s="25"/>
       <c r="F1" s="25"/>
     </row>
-    <row r="2" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1176,7 +1396,7 @@
       <c r="E2" s="27"/>
       <c r="F2" s="28"/>
     </row>
-    <row r="3" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="26.25">
       <c r="A3" s="29" t="s">
         <v>2</v>
       </c>
@@ -1186,7 +1406,7 @@
       <c r="E3" s="30"/>
       <c r="F3" s="31"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1203,7 +1423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1219,7 +1439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1235,7 +1455,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="30">
       <c r="A7" s="9" t="s">
         <v>14</v>
       </c>
@@ -1255,7 +1475,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="32" t="s">
         <v>20</v>
       </c>
@@ -1267,7 +1487,7 @@
       </c>
       <c r="F8" s="12"/>
     </row>
-    <row r="9" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="23.25" customHeight="true">
       <c r="A9" s="13" t="s">
         <v>22</v>
       </c>
@@ -1281,7 +1501,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="19" t="s">
         <v>22</v>
       </c>
@@ -1299,285 +1519,2038 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+    <row r="11">
+      <c r="A11" s="38">
         <v>1</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="38">
+        <v>59</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="38">
         <v>2</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="35" t="s">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="38">
+        <v>86</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38">
+        <v>3</v>
+      </c>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="38">
+        <v>53</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="38">
+        <v>4</v>
+      </c>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="38">
+        <v>69</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="38">
+        <v>5</v>
+      </c>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="38">
+        <v>61</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="38">
+        <v>6</v>
+      </c>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="38">
+        <v>57</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="38">
+        <v>7</v>
+      </c>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="38">
+        <v>175</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="38">
+        <v>8</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="38">
+        <v>59</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="38">
+        <v>9</v>
+      </c>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="38">
+        <v>76</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="38">
+        <v>10</v>
+      </c>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="38">
+        <v>52</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="38">
+        <v>11</v>
+      </c>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="38">
+        <v>73</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="38">
+        <v>12</v>
+      </c>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="38">
+        <v>64</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="38">
+        <v>13</v>
+      </c>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="38">
+        <v>47</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38">
+        <v>14</v>
+      </c>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="38">
+        <v>115</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="38">
+        <v>15</v>
+      </c>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="38">
+        <v>103</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="38">
+        <v>16</v>
+      </c>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="38">
+        <v>40</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="38">
+        <v>17</v>
+      </c>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="38">
+        <v>88</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="38">
+        <v>18</v>
+      </c>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="38">
+        <v>117</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="38">
+        <v>19</v>
+      </c>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="38">
+        <v>127</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="38">
+        <v>20</v>
+      </c>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="38">
+        <v>41</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="38">
+        <v>21</v>
+      </c>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="38">
+        <v>91</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="38">
+        <v>22</v>
+      </c>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" s="38">
+        <v>87</v>
+      </c>
+      <c r="F32" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="38">
+        <v>23</v>
+      </c>
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" s="38">
+        <v>79</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="38">
+        <v>24</v>
+      </c>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="38">
+        <v>57</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="38">
+        <v>25</v>
+      </c>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="38">
+        <v>58</v>
+      </c>
+      <c r="F35" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="38">
         <v>26</v>
       </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="23">
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" s="38">
+        <v>49</v>
+      </c>
+      <c r="F36" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="38">
+        <v>27</v>
+      </c>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="38">
+        <v>126</v>
+      </c>
+      <c r="F37" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="38">
+        <v>28</v>
+      </c>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="38">
+        <v>76</v>
+      </c>
+      <c r="F38" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="38">
+        <v>29</v>
+      </c>
+      <c r="B39" s="38"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="38">
+        <v>61</v>
+      </c>
+      <c r="F39" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="38">
+        <v>30</v>
+      </c>
+      <c r="B40" s="38"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="38">
+        <v>1</v>
+      </c>
+      <c r="F40" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="38">
+        <v>31</v>
+      </c>
+      <c r="B41" s="38"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" s="38">
+        <v>116</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="38">
+        <v>32</v>
+      </c>
+      <c r="B42" s="38"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="38">
+        <v>61</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="38">
+        <v>33</v>
+      </c>
+      <c r="B43" s="38"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="E43" s="38">
+        <v>45</v>
+      </c>
+      <c r="F43" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="38">
+        <v>34</v>
+      </c>
+      <c r="B44" s="38"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" s="38">
+        <v>12</v>
+      </c>
+      <c r="F44" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="38">
+        <v>35</v>
+      </c>
+      <c r="B45" s="38"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="38">
+        <v>78</v>
+      </c>
+      <c r="F45" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="38">
+        <v>36</v>
+      </c>
+      <c r="B46" s="38"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="E46" s="38">
+        <v>123</v>
+      </c>
+      <c r="F46" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="38">
+        <v>37</v>
+      </c>
+      <c r="B47" s="38"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="38">
+        <v>161</v>
+      </c>
+      <c r="F47" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="38">
+        <v>38</v>
+      </c>
+      <c r="B48" s="38"/>
+      <c r="C48" s="38"/>
+      <c r="D48" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="E48" s="38">
+        <v>103</v>
+      </c>
+      <c r="F48" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="38">
+        <v>39</v>
+      </c>
+      <c r="B49" s="38"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="E49" s="38">
+        <v>41</v>
+      </c>
+      <c r="F49" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="38">
+        <v>40</v>
+      </c>
+      <c r="B50" s="38"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="38">
+        <v>55</v>
+      </c>
+      <c r="F50" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="38">
+        <v>41</v>
+      </c>
+      <c r="B51" s="38"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="E51" s="38">
+        <v>110</v>
+      </c>
+      <c r="F51" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="38">
+        <v>42</v>
+      </c>
+      <c r="B52" s="38"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="38">
+        <v>50</v>
+      </c>
+      <c r="F52" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="38">
+        <v>43</v>
+      </c>
+      <c r="B53" s="38"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="E53" s="38">
+        <v>63</v>
+      </c>
+      <c r="F53" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="38">
+        <v>44</v>
+      </c>
+      <c r="B54" s="38"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="E54" s="38">
+        <v>49</v>
+      </c>
+      <c r="F54" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="38">
+        <v>45</v>
+      </c>
+      <c r="B55" s="38"/>
+      <c r="C55" s="38"/>
+      <c r="D55" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="E55" s="38">
+        <v>87</v>
+      </c>
+      <c r="F55" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="38">
+        <v>46</v>
+      </c>
+      <c r="B56" s="38"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="E56" s="38">
+        <v>42</v>
+      </c>
+      <c r="F56" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="38">
+        <v>47</v>
+      </c>
+      <c r="B57" s="38"/>
+      <c r="C57" s="38"/>
+      <c r="D57" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="E57" s="38">
+        <v>97</v>
+      </c>
+      <c r="F57" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="38">
+        <v>48</v>
+      </c>
+      <c r="B58" s="38"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="E58" s="38">
+        <v>90</v>
+      </c>
+      <c r="F58" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="38">
+        <v>49</v>
+      </c>
+      <c r="B59" s="38"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="E59" s="38">
+        <v>143</v>
+      </c>
+      <c r="F59" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="38">
+        <v>50</v>
+      </c>
+      <c r="B60" s="38"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="E60" s="38">
+        <v>92</v>
+      </c>
+      <c r="F60" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="38">
+        <v>51</v>
+      </c>
+      <c r="B61" s="38"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E61" s="38">
+        <v>108</v>
+      </c>
+      <c r="F61" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="38">
+        <v>52</v>
+      </c>
+      <c r="B62" s="38"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="E62" s="38">
+        <v>73</v>
+      </c>
+      <c r="F62" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="38">
+        <v>53</v>
+      </c>
+      <c r="B63" s="38"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="E63" s="38">
+        <v>45</v>
+      </c>
+      <c r="F63" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="38">
+        <v>54</v>
+      </c>
+      <c r="B64" s="38"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="E64" s="38">
+        <v>143</v>
+      </c>
+      <c r="F64" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="38">
+        <v>55</v>
+      </c>
+      <c r="B65" s="38"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="E65" s="38">
+        <v>56</v>
+      </c>
+      <c r="F65" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="38">
+        <v>56</v>
+      </c>
+      <c r="B66" s="38"/>
+      <c r="C66" s="38"/>
+      <c r="D66" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E66" s="38">
+        <v>69</v>
+      </c>
+      <c r="F66" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="38">
+        <v>57</v>
+      </c>
+      <c r="B67" s="38"/>
+      <c r="C67" s="38"/>
+      <c r="D67" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="E67" s="38">
+        <v>46</v>
+      </c>
+      <c r="F67" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="38">
+        <v>58</v>
+      </c>
+      <c r="B68" s="38"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="E68" s="38">
+        <v>34</v>
+      </c>
+      <c r="F68" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="38">
+        <v>59</v>
+      </c>
+      <c r="B69" s="38"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="E69" s="38">
+        <v>22</v>
+      </c>
+      <c r="F69" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="38">
+        <v>60</v>
+      </c>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="E70" s="38">
+        <v>69</v>
+      </c>
+      <c r="F70" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="38">
+        <v>61</v>
+      </c>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="E71" s="38">
+        <v>139</v>
+      </c>
+      <c r="F71" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="38">
+        <v>62</v>
+      </c>
+      <c r="B72" s="38"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="E72" s="38">
+        <v>68</v>
+      </c>
+      <c r="F72" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="38">
+        <v>63</v>
+      </c>
+      <c r="B73" s="38"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="E73" s="38">
+        <v>84</v>
+      </c>
+      <c r="F73" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="38">
+        <v>64</v>
+      </c>
+      <c r="B74" s="38"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="E74" s="38">
+        <v>142</v>
+      </c>
+      <c r="F74" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="38">
+        <v>65</v>
+      </c>
+      <c r="B75" s="38"/>
+      <c r="C75" s="38"/>
+      <c r="D75" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="E75" s="38">
+        <v>111</v>
+      </c>
+      <c r="F75" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="38">
+        <v>66</v>
+      </c>
+      <c r="B76" s="38"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="E76" s="38">
+        <v>55</v>
+      </c>
+      <c r="F76" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="38">
+        <v>67</v>
+      </c>
+      <c r="B77" s="38"/>
+      <c r="C77" s="38"/>
+      <c r="D77" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="E77" s="38">
+        <v>77</v>
+      </c>
+      <c r="F77" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="38">
+        <v>68</v>
+      </c>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="E78" s="38">
+        <v>192</v>
+      </c>
+      <c r="F78" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="38">
+        <v>69</v>
+      </c>
+      <c r="B79" s="38"/>
+      <c r="C79" s="38"/>
+      <c r="D79" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="E79" s="38">
+        <v>100</v>
+      </c>
+      <c r="F79" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="38">
+        <v>70</v>
+      </c>
+      <c r="B80" s="38"/>
+      <c r="C80" s="38"/>
+      <c r="D80" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="E80" s="38">
+        <v>72</v>
+      </c>
+      <c r="F80" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="38">
+        <v>71</v>
+      </c>
+      <c r="B81" s="38"/>
+      <c r="C81" s="38"/>
+      <c r="D81" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="E81" s="38">
+        <v>29</v>
+      </c>
+      <c r="F81" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="38">
+        <v>72</v>
+      </c>
+      <c r="B82" s="38"/>
+      <c r="C82" s="38"/>
+      <c r="D82" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="E82" s="38">
+        <v>89</v>
+      </c>
+      <c r="F82" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="38">
+        <v>73</v>
+      </c>
+      <c r="B83" s="38"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="E83" s="38">
+        <v>100</v>
+      </c>
+      <c r="F83" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="38">
+        <v>74</v>
+      </c>
+      <c r="B84" s="38"/>
+      <c r="C84" s="38"/>
+      <c r="D84" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="E84" s="38">
+        <v>146</v>
+      </c>
+      <c r="F84" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="38">
+        <v>75</v>
+      </c>
+      <c r="B85" s="38"/>
+      <c r="C85" s="38"/>
+      <c r="D85" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="E85" s="38">
+        <v>49</v>
+      </c>
+      <c r="F85" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="38">
+        <v>76</v>
+      </c>
+      <c r="B86" s="38"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="E86" s="38">
+        <v>85</v>
+      </c>
+      <c r="F86" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="38">
+        <v>77</v>
+      </c>
+      <c r="B87" s="38"/>
+      <c r="C87" s="38"/>
+      <c r="D87" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="E87" s="38">
+        <v>93</v>
+      </c>
+      <c r="F87" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="38">
+        <v>78</v>
+      </c>
+      <c r="B88" s="38"/>
+      <c r="C88" s="38"/>
+      <c r="D88" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="E88" s="38">
+        <v>80</v>
+      </c>
+      <c r="F88" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="38">
+        <v>79</v>
+      </c>
+      <c r="B89" s="38"/>
+      <c r="C89" s="38"/>
+      <c r="D89" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="E89" s="38">
+        <v>23</v>
+      </c>
+      <c r="F89" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="38">
+        <v>80</v>
+      </c>
+      <c r="B90" s="38"/>
+      <c r="C90" s="38"/>
+      <c r="D90" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="E90" s="38">
+        <v>74</v>
+      </c>
+      <c r="F90" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="38">
+        <v>81</v>
+      </c>
+      <c r="B91" s="38"/>
+      <c r="C91" s="38"/>
+      <c r="D91" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="E91" s="38">
+        <v>87</v>
+      </c>
+      <c r="F91" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="38">
+        <v>82</v>
+      </c>
+      <c r="B92" s="38"/>
+      <c r="C92" s="38"/>
+      <c r="D92" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E92" s="38">
+        <v>96</v>
+      </c>
+      <c r="F92" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="38">
+        <v>83</v>
+      </c>
+      <c r="B93" s="38"/>
+      <c r="C93" s="38"/>
+      <c r="D93" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="E93" s="38">
+        <v>73</v>
+      </c>
+      <c r="F93" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="38">
+        <v>84</v>
+      </c>
+      <c r="B94" s="38"/>
+      <c r="C94" s="38"/>
+      <c r="D94" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="E94" s="38">
+        <v>46</v>
+      </c>
+      <c r="F94" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="38">
+        <v>85</v>
+      </c>
+      <c r="B95" s="38"/>
+      <c r="C95" s="38"/>
+      <c r="D95" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="E95" s="38">
+        <v>88</v>
+      </c>
+      <c r="F95" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="38">
+        <v>86</v>
+      </c>
+      <c r="B96" s="38"/>
+      <c r="C96" s="38"/>
+      <c r="D96" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="E96" s="38">
+        <v>51</v>
+      </c>
+      <c r="F96" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="38">
+        <v>87</v>
+      </c>
+      <c r="B97" s="38"/>
+      <c r="C97" s="38"/>
+      <c r="D97" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="E97" s="38">
+        <v>90</v>
+      </c>
+      <c r="F97" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="38">
+        <v>88</v>
+      </c>
+      <c r="B98" s="38"/>
+      <c r="C98" s="38"/>
+      <c r="D98" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="E98" s="38">
+        <v>132</v>
+      </c>
+      <c r="F98" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="38">
+        <v>89</v>
+      </c>
+      <c r="B99" s="38"/>
+      <c r="C99" s="38"/>
+      <c r="D99" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="E99" s="38">
+        <v>94</v>
+      </c>
+      <c r="F99" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="38">
+        <v>90</v>
+      </c>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="E100" s="38">
+        <v>61</v>
+      </c>
+      <c r="F100" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="38">
+        <v>91</v>
+      </c>
+      <c r="B101" s="38"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="E101" s="38">
+        <v>70</v>
+      </c>
+      <c r="F101" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="38">
+        <v>92</v>
+      </c>
+      <c r="B102" s="38"/>
+      <c r="C102" s="38"/>
+      <c r="D102" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="E102" s="38">
+        <v>124</v>
+      </c>
+      <c r="F102" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="38">
+        <v>93</v>
+      </c>
+      <c r="B103" s="38"/>
+      <c r="C103" s="38"/>
+      <c r="D103" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="E103" s="38">
+        <v>97</v>
+      </c>
+      <c r="F103" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="38">
+        <v>94</v>
+      </c>
+      <c r="B104" s="38"/>
+      <c r="C104" s="38"/>
+      <c r="D104" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="E104" s="38">
+        <v>83</v>
+      </c>
+      <c r="F104" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="38">
+        <v>95</v>
+      </c>
+      <c r="B105" s="38"/>
+      <c r="C105" s="38"/>
+      <c r="D105" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="E105" s="38">
+        <v>55</v>
+      </c>
+      <c r="F105" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="38">
+        <v>96</v>
+      </c>
+      <c r="B106" s="38"/>
+      <c r="C106" s="38"/>
+      <c r="D106" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="E106" s="38">
+        <v>73</v>
+      </c>
+      <c r="F106" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="38">
+        <v>97</v>
+      </c>
+      <c r="B107" s="38"/>
+      <c r="C107" s="38"/>
+      <c r="D107" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="E107" s="38">
+        <v>101</v>
+      </c>
+      <c r="F107" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="38">
+        <v>98</v>
+      </c>
+      <c r="B108" s="38"/>
+      <c r="C108" s="38"/>
+      <c r="D108" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="E108" s="38">
+        <v>63</v>
+      </c>
+      <c r="F108" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="38">
+        <v>99</v>
+      </c>
+      <c r="B109" s="38"/>
+      <c r="C109" s="38"/>
+      <c r="D109" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="E109" s="38">
+        <v>15</v>
+      </c>
+      <c r="F109" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="38">
+        <v>100</v>
+      </c>
+      <c r="B110" s="38"/>
+      <c r="C110" s="38"/>
+      <c r="D110" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E110" s="38">
+        <v>35</v>
+      </c>
+      <c r="F110" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="38">
+        <v>101</v>
+      </c>
+      <c r="B111" s="38"/>
+      <c r="C111" s="38"/>
+      <c r="D111" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="E111" s="38">
+        <v>144</v>
+      </c>
+      <c r="F111" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="38">
+        <v>102</v>
+      </c>
+      <c r="B112" s="38"/>
+      <c r="C112" s="38"/>
+      <c r="D112" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="E112" s="38">
+        <v>106</v>
+      </c>
+      <c r="F112" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="38">
+        <v>103</v>
+      </c>
+      <c r="B113" s="38"/>
+      <c r="C113" s="38"/>
+      <c r="D113" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="E113" s="38">
+        <v>154</v>
+      </c>
+      <c r="F113" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="38">
+        <v>104</v>
+      </c>
+      <c r="B114" s="38"/>
+      <c r="C114" s="38"/>
+      <c r="D114" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="E114" s="38">
+        <v>84</v>
+      </c>
+      <c r="F114" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="38">
+        <v>105</v>
+      </c>
+      <c r="B115" s="38"/>
+      <c r="C115" s="38"/>
+      <c r="D115" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="E115" s="38">
+        <v>134</v>
+      </c>
+      <c r="F115" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="38">
+        <v>106</v>
+      </c>
+      <c r="B116" s="38"/>
+      <c r="C116" s="38"/>
+      <c r="D116" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="E116" s="38">
+        <v>99</v>
+      </c>
+      <c r="F116" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="38">
+        <v>107</v>
+      </c>
+      <c r="B117" s="38"/>
+      <c r="C117" s="38"/>
+      <c r="D117" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="E117" s="38">
+        <v>49</v>
+      </c>
+      <c r="F117" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="38">
+        <v>108</v>
+      </c>
+      <c r="B118" s="38"/>
+      <c r="C118" s="38"/>
+      <c r="D118" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="E118" s="38">
+        <v>90</v>
+      </c>
+      <c r="F118" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="38">
+        <v>109</v>
+      </c>
+      <c r="B119" s="38"/>
+      <c r="C119" s="38"/>
+      <c r="D119" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="E119" s="38">
+        <v>6</v>
+      </c>
+      <c r="F119" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="38">
+        <v>110</v>
+      </c>
+      <c r="B120" s="38"/>
+      <c r="C120" s="38"/>
+      <c r="D120" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="E120" s="38">
+        <v>105</v>
+      </c>
+      <c r="F120" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="38">
+        <v>111</v>
+      </c>
+      <c r="B121" s="38"/>
+      <c r="C121" s="38"/>
+      <c r="D121" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="E121" s="38">
+        <v>65</v>
+      </c>
+      <c r="F121" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="38">
+        <v>112</v>
+      </c>
+      <c r="B122" s="38"/>
+      <c r="C122" s="38"/>
+      <c r="D122" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="E122" s="38">
+        <v>99</v>
+      </c>
+      <c r="F122" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="38">
+        <v>113</v>
+      </c>
+      <c r="B123" s="38"/>
+      <c r="C123" s="38"/>
+      <c r="D123" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="E123" s="38">
+        <v>42</v>
+      </c>
+      <c r="F123" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="38">
+        <v>114</v>
+      </c>
+      <c r="B124" s="38"/>
+      <c r="C124" s="38"/>
+      <c r="D124" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="E124" s="38">
+        <v>52</v>
+      </c>
+      <c r="F124" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="38">
+        <v>115</v>
+      </c>
+      <c r="B125" s="38"/>
+      <c r="C125" s="38"/>
+      <c r="D125" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="E125" s="38">
+        <v>149</v>
+      </c>
+      <c r="F125" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="38">
+        <v>116</v>
+      </c>
+      <c r="B126" s="38"/>
+      <c r="C126" s="38"/>
+      <c r="D126" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="E126" s="38">
+        <v>90</v>
+      </c>
+      <c r="F126" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="38">
+        <v>117</v>
+      </c>
+      <c r="B127" s="38"/>
+      <c r="C127" s="38"/>
+      <c r="D127" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="E127" s="38">
+        <v>156</v>
+      </c>
+      <c r="F127" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="38">
+        <v>118</v>
+      </c>
+      <c r="B128" s="38"/>
+      <c r="C128" s="38"/>
+      <c r="D128" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="E128" s="38">
+        <v>86</v>
+      </c>
+      <c r="F128" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="38">
+        <v>119</v>
+      </c>
+      <c r="B129" s="38"/>
+      <c r="C129" s="38"/>
+      <c r="D129" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="E129" s="38">
+        <v>194</v>
+      </c>
+      <c r="F129" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="38">
+        <v>120</v>
+      </c>
+      <c r="B130" s="38"/>
+      <c r="C130" s="38"/>
+      <c r="D130" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="E130" s="38">
+        <v>65</v>
+      </c>
+      <c r="F130" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="38">
+        <v>121</v>
+      </c>
+      <c r="B131" s="38"/>
+      <c r="C131" s="38"/>
+      <c r="D131" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="E131" s="38">
+        <v>86</v>
+      </c>
+      <c r="F131" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="38">
+        <v>122</v>
+      </c>
+      <c r="B132" s="38"/>
+      <c r="C132" s="38"/>
+      <c r="D132" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="E132" s="38">
+        <v>100</v>
+      </c>
+      <c r="F132" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="38">
+        <v>123</v>
+      </c>
+      <c r="B133" s="38"/>
+      <c r="C133" s="38"/>
+      <c r="D133" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="E133" s="38">
+        <v>48</v>
+      </c>
+      <c r="F133" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="38">
+        <v>124</v>
+      </c>
+      <c r="B134" s="38"/>
+      <c r="C134" s="38"/>
+      <c r="D134" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="E134" s="38">
+        <v>104</v>
+      </c>
+      <c r="F134" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" s="3">
+        <v>1</v>
+      </c>
+      <c r="B135" s="18"/>
+      <c r="C135" s="24"/>
+      <c r="D135" s="24"/>
+      <c r="E135" s="24"/>
+      <c r="F135" s="3"/>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" s="3">
+        <v>2</v>
+      </c>
+      <c r="B136" s="18"/>
+      <c r="C136" s="24"/>
+      <c r="D136" s="24"/>
+      <c r="E136" s="24"/>
+      <c r="F136" s="3"/>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B137" s="36"/>
+      <c r="C137" s="36"/>
+      <c r="D137" s="37"/>
+      <c r="E137" s="23">
         <v>0</v>
       </c>
-      <c r="F13" s="23"/>
+      <c r="F137" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A137:D137"/>
+    <mergeCell ref="B11:B134"/>
   </mergeCells>
-  <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="25" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D2">
-    <cfRule type="aboveAverage" dxfId="24" priority="4" aboveAverage="0"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="7"/>
-    <cfRule type="aboveAverage" dxfId="22" priority="8" aboveAverage="0"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D3">
-    <cfRule type="duplicateValues" dxfId="20" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D7">
-    <cfRule type="duplicateValues" dxfId="19" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D12">
-    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D6">
-    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D7">
-    <cfRule type="duplicateValues" dxfId="15" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D13">
-    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349B22A9-497E-49C7-A8BD-06C74781CB78}">
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" customWidth="1"/>
-    <col min="6" max="6" width="25.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-    </row>
-    <row r="2" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="28"/>
-    </row>
-    <row r="3" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A3" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="31"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="str">
-        <f>[1]SOURCE!$A$3</f>
-        <v>2026-04-03</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="12"/>
-    </row>
-    <row r="9" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="21">
-        <v>0</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>1</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>2</v>
-      </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="23">
-        <v>0</v>
-      </c>
-      <c r="F13" s="23"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A13:D13"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D1">
+  <conditionalFormatting sqref="D1:D1">
     <cfRule type="duplicateValues" dxfId="12" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D2">
-    <cfRule type="aboveAverage" dxfId="11" priority="4" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="11" priority="4" aboveAverage="false"/>
     <cfRule type="duplicateValues" dxfId="10" priority="7"/>
-    <cfRule type="aboveAverage" dxfId="9" priority="8" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="9" priority="8" aboveAverage="false"/>
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D3">
@@ -1586,19 +3559,19 @@
   <conditionalFormatting sqref="D1:D7">
     <cfRule type="duplicateValues" dxfId="6" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D12">
+  <conditionalFormatting sqref="D1:D136">
     <cfRule type="duplicateValues" dxfId="5" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="D2:D2">
     <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6">
     <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7">
+  <conditionalFormatting sqref="D7:D7">
     <cfRule type="duplicateValues" dxfId="2" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D13">
+  <conditionalFormatting sqref="D137:D137">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
